--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -866,11 +866,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -904,14 +904,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>116.666666666667</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" s="15">
-        <v>36.363636363636</v>
+        <v>58.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="M16" s="15">
-        <v>-57.142857142857</v>
+        <v>-52.5</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.179487179487</v>
+        <v>-86.029411764705</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-22.222222222222</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>-28.125</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I17" s="14">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J17" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K17" s="15">
-        <v>-20</v>
+        <v>-4.444444444444</v>
       </c>
       <c r="L17" s="15">
-        <v>-15.789473684210</v>
+        <v>-4.444444444444</v>
       </c>
       <c r="M17" s="15">
-        <v>23.076923076923</v>
+        <v>43.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-54.929577464788</v>
+        <v>-50.574712643678</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1031,28 +1031,28 @@
         <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K18" s="15">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>50</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.545454545454</v>
+        <v>-79.166666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.217391304347</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>400</v>
       </c>
       <c r="F19" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>15.625</v>
+        <v>60</v>
       </c>
       <c r="I19" s="14">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="J19" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K19" s="15">
-        <v>20.930232558139</v>
+        <v>50</v>
       </c>
       <c r="L19" s="15">
-        <v>85.714285714285</v>
+        <v>91.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>-23.529411764705</v>
+        <v>-6.756756756756</v>
       </c>
       <c r="N19" s="15">
-        <v>-72.916666666666</v>
+        <v>-68.202764976958</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G20" s="14">
         <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>-8.333333333333</v>
+        <v>25</v>
       </c>
       <c r="I20" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J20" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K20" s="15">
-        <v>-40.909090909090</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-45.833333333333</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="M20" s="15">
-        <v>-58.064516129032</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.048128342246</v>
+        <v>-90.995260663507</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.384615384615</v>
+        <v>200</v>
       </c>
       <c r="F21" s="17">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.123595505617</v>
+        <v>29.870129870129</v>
       </c>
       <c r="I21" s="17">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="J21" s="17">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.612903225806</v>
+        <v>18.382352941176</v>
       </c>
       <c r="L21" s="18">
-        <v>7.964601769911</v>
+        <v>19.259259259259</v>
       </c>
       <c r="M21" s="18">
-        <v>-40.776699029126</v>
+        <v>-29.074889867841</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.952662721893</v>
+        <v>-79.332477535301</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1226,29 +1226,29 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="14">
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-100</v>
       </c>
       <c r="I23" s="14">
         <v>1</v>
       </c>
-      <c r="J23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>21</v>
+      <c r="J23" s="14">
+        <v>1</v>
+      </c>
+      <c r="K23" s="15">
+        <v>0</v>
       </c>
       <c r="L23" s="15">
         <v>-50</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>62.5</v>
       </c>
       <c r="F24" s="14">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G24" s="14">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="H24" s="15">
-        <v>36.923076923076</v>
+        <v>44.642857142857</v>
       </c>
       <c r="I24" s="14">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="J24" s="14">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K24" s="15">
-        <v>48.780487804878</v>
+        <v>48.979591836734</v>
       </c>
       <c r="L24" s="15">
-        <v>10.909090909090</v>
+        <v>5.035971223021</v>
       </c>
       <c r="M24" s="15">
-        <v>37.078651685393</v>
+        <v>30.357142857142</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>50</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I25" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J25" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K25" s="15">
-        <v>42.857142857142</v>
+        <v>18.518518518518</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.076923076923</v>
+        <v>-31.914893617021</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F26" s="14">
         <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H26" s="15">
-        <v>8.571428571428</v>
+        <v>-25.490196078431</v>
       </c>
       <c r="I26" s="14">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="J26" s="14">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.084745762711</v>
+        <v>-11.25</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.754385964912</v>
+        <v>5.970149253731</v>
       </c>
       <c r="M26" s="15">
-        <v>-22.222222222222</v>
+        <v>-19.318181818181</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,14 +1396,14 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="I28" s="14">
         <v>2</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>-77.777777777777</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L28" s="15">
         <v>-60</v>
@@ -1482,7 +1482,7 @@
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1523,7 +1523,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1561,7 +1561,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1570,7 +1570,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -898,11 +898,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -917,10 +917,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L15" s="15">
         <v>-50</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>133.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J16" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K16" s="15">
-        <v>58.333333333333</v>
+        <v>46.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>18.75</v>
+        <v>37.5</v>
       </c>
       <c r="M16" s="15">
-        <v>-52.5</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.029411764705</v>
+        <v>-86.419753086419</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F17" s="14">
+        <v>31</v>
+      </c>
+      <c r="G17" s="14">
         <v>28</v>
       </c>
-      <c r="G17" s="14">
-        <v>29</v>
-      </c>
       <c r="H17" s="15">
-        <v>-3.448275862068</v>
+        <v>10.714285714285</v>
       </c>
       <c r="I17" s="14">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J17" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.444444444444</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-4.444444444444</v>
+        <v>-1.923076923076</v>
       </c>
       <c r="M17" s="15">
-        <v>43.333333333333</v>
+        <v>37.837837837837</v>
       </c>
       <c r="N17" s="15">
-        <v>-50.574712643678</v>
+        <v>-48.484848484848</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I18" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J18" s="14">
         <v>6</v>
       </c>
       <c r="K18" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L18" s="15">
-        <v>11.111111111111</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.166666666666</v>
+        <v>-76.470588235294</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.909090909090</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>400</v>
+        <v>-10</v>
       </c>
       <c r="F19" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>60</v>
+        <v>53.571428571428</v>
       </c>
       <c r="I19" s="14">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="J19" s="14">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="K19" s="15">
-        <v>50</v>
+        <v>39.285714285714</v>
       </c>
       <c r="L19" s="15">
-        <v>91.666666666666</v>
+        <v>105.263157894737</v>
       </c>
       <c r="M19" s="15">
-        <v>-6.756756756756</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N19" s="15">
-        <v>-68.202764976958</v>
+        <v>-69.169960474308</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>25</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I20" s="14">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J20" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>-20.833333333333</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="L20" s="15">
-        <v>-29.629629629629</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="M20" s="15">
-        <v>-42.424242424242</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.995260663507</v>
+        <v>-88.559322033898</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="F21" s="17">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G21" s="17">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H21" s="18">
-        <v>29.870129870129</v>
+        <v>34.567901234567</v>
       </c>
       <c r="I21" s="17">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="J21" s="17">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="K21" s="18">
-        <v>18.382352941176</v>
+        <v>19.375</v>
       </c>
       <c r="L21" s="18">
-        <v>19.259259259259</v>
+        <v>29.054054054054</v>
       </c>
       <c r="M21" s="18">
-        <v>-29.074889867841</v>
+        <v>-27.099236641221</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.332477535301</v>
+        <v>-78.515185601799</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1226,11 +1226,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E24" s="15">
-        <v>62.5</v>
+        <v>81.818181818181</v>
       </c>
       <c r="F24" s="14">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H24" s="15">
-        <v>44.642857142857</v>
+        <v>39.215686274509</v>
       </c>
       <c r="I24" s="14">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="J24" s="14">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="K24" s="15">
-        <v>48.979591836734</v>
+        <v>52.293577981651</v>
       </c>
       <c r="L24" s="15">
-        <v>5.035971223021</v>
+        <v>3.75</v>
       </c>
       <c r="M24" s="15">
-        <v>30.357142857142</v>
+        <v>22.058823529411</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>4</v>
+      </c>
+      <c r="D25" s="14">
         <v>2</v>
       </c>
-      <c r="D25" s="14">
-        <v>6</v>
-      </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H25" s="15">
-        <v>5.555555555555</v>
+        <v>-6.25</v>
       </c>
       <c r="I25" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J25" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K25" s="15">
-        <v>18.518518518518</v>
+        <v>24.137931034482</v>
       </c>
       <c r="L25" s="15">
-        <v>-31.914893617021</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-23.809523809523</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G26" s="14">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>-25.490196078431</v>
+        <v>6.818181818181</v>
       </c>
       <c r="I26" s="14">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="J26" s="14">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.25</v>
+        <v>-6.593406593406</v>
       </c>
       <c r="L26" s="15">
-        <v>5.970149253731</v>
+        <v>-1.162790697674</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.318181818181</v>
+        <v>-9.574468085106</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1409,13 +1409,13 @@
         <v>1</v>
       </c>
       <c r="J27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1432,7 +1432,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
@@ -1450,10 +1450,10 @@
         <v>2</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="L28" s="15">
         <v>-60</v>
@@ -1561,7 +1561,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1622,11 +1622,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -863,8 +863,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -872,23 +872,23 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -898,17 +898,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
         <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="I16" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K16" s="15">
-        <v>46.666666666666</v>
+        <v>41.176470588235</v>
       </c>
       <c r="L16" s="15">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-48.936170212766</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.419753086419</v>
+        <v>-87.027027027027</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>16.666666666666</v>
+        <v>140</v>
       </c>
       <c r="F17" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G17" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H17" s="15">
-        <v>10.714285714285</v>
+        <v>48</v>
       </c>
       <c r="I17" s="14">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="J17" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L17" s="15">
-        <v>-1.923076923076</v>
+        <v>3.225806451612</v>
       </c>
       <c r="M17" s="15">
-        <v>37.837837837837</v>
+        <v>45.454545454545</v>
       </c>
       <c r="N17" s="15">
-        <v>-48.484848484848</v>
+        <v>-40.186915887850</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1028,31 +1028,31 @@
         <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
         <v>2</v>
       </c>
       <c r="H18" s="15">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="I18" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J18" s="14">
         <v>6</v>
       </c>
       <c r="K18" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L18" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-76.470588235294</v>
+        <v>-74.137931034482</v>
       </c>
       <c r="N18" s="15">
-        <v>-90</v>
+        <v>-89.208633093525</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-10</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>53.571428571428</v>
+        <v>37.931034482758</v>
       </c>
       <c r="I19" s="14">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J19" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K19" s="15">
-        <v>39.285714285714</v>
+        <v>35.483870967741</v>
       </c>
       <c r="L19" s="15">
-        <v>105.263157894737</v>
+        <v>90.909090909090</v>
       </c>
       <c r="M19" s="15">
-        <v>-14.285714285714</v>
+        <v>-16</v>
       </c>
       <c r="N19" s="15">
-        <v>-69.169960474308</v>
+        <v>-71.134020618556</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>38.461538461538</v>
+        <v>50</v>
       </c>
       <c r="I20" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.571428571428</v>
+        <v>-6.25</v>
       </c>
       <c r="L20" s="15">
-        <v>-12.903225806451</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>-27.027027027027</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.559322033898</v>
+        <v>-88.461538461538</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>25</v>
+        <v>64.705882352941</v>
       </c>
       <c r="F21" s="17">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G21" s="17">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>34.567901234567</v>
+        <v>48.101265822784</v>
       </c>
       <c r="I21" s="17">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="J21" s="17">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="K21" s="18">
-        <v>19.375</v>
+        <v>23.728813559322</v>
       </c>
       <c r="L21" s="18">
-        <v>29.054054054054</v>
+        <v>28.070175438596</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.099236641221</v>
+        <v>-25</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.515185601799</v>
+        <v>-78.121878121878</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>81.818181818181</v>
+        <v>-35</v>
       </c>
       <c r="F24" s="14">
         <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H24" s="15">
-        <v>39.215686274509</v>
+        <v>24.561403508771</v>
       </c>
       <c r="I24" s="14">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="J24" s="14">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="K24" s="15">
-        <v>52.293577981651</v>
+        <v>39.534883720930</v>
       </c>
       <c r="L24" s="15">
-        <v>3.75</v>
+        <v>2.857142857142</v>
       </c>
       <c r="M24" s="15">
-        <v>22.058823529411</v>
+        <v>24.137931034482</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>-6.25</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I25" s="14">
+        <v>39</v>
+      </c>
+      <c r="J25" s="14">
         <v>36</v>
       </c>
-      <c r="J25" s="14">
-        <v>29</v>
-      </c>
       <c r="K25" s="15">
-        <v>24.137931034482</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>-30.769230769230</v>
+        <v>-26.415094339622</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="H26" s="15">
-        <v>6.818181818181</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="J26" s="14">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.593406593406</v>
+        <v>-10.377358490566</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.162790697674</v>
+        <v>-5</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.574468085106</v>
+        <v>-15.178571428571</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,32 +1390,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0</v>
+      </c>
+      <c r="I27" s="14">
         <v>2</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="14">
-        <v>1</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
+      </c>
+      <c r="F28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>1</v>
-      </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-88.888888888888</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-85.714285714285</v>
+        <v>-80</v>
       </c>
       <c r="L28" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1481,11 +1481,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1522,11 +1522,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
@@ -1560,8 +1560,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -888,15 +888,15 @@
         <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -904,32 +904,32 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>-92.307692307692</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J16" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>41.176470588235</v>
+        <v>38.095238095238</v>
       </c>
       <c r="L16" s="15">
-        <v>33.333333333333</v>
+        <v>31.818181818181</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.936170212766</v>
+        <v>-46.296296296296</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.027027027027</v>
+        <v>-85.853658536585</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>140</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F17" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G17" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H17" s="15">
-        <v>48</v>
+        <v>47.826086956521</v>
       </c>
       <c r="I17" s="14">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J17" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K17" s="15">
-        <v>14.285714285714</v>
+        <v>6.349206349206</v>
       </c>
       <c r="L17" s="15">
-        <v>3.225806451612</v>
+        <v>-2.898550724637</v>
       </c>
       <c r="M17" s="15">
-        <v>45.454545454545</v>
+        <v>36.734693877551</v>
       </c>
       <c r="N17" s="15">
-        <v>-40.186915887850</v>
+        <v>-40.707964601769</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
         <v>2</v>
       </c>
       <c r="H18" s="15">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="I18" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K18" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L18" s="15">
-        <v>66.666666666666</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M18" s="15">
-        <v>-74.137931034482</v>
+        <v>-78.461538461538</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.208633093525</v>
+        <v>-90.967741935483</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1063,60 +1063,60 @@
         <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>37.931034482758</v>
+        <v>39.285714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J19" s="14">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K19" s="15">
-        <v>35.483870967741</v>
+        <v>30.985915492957</v>
       </c>
       <c r="L19" s="15">
-        <v>90.909090909090</v>
+        <v>86</v>
       </c>
       <c r="M19" s="15">
-        <v>-16</v>
+        <v>-14.678899082568</v>
       </c>
       <c r="N19" s="15">
-        <v>-71.134020618556</v>
+        <v>-71.028037383177</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>3</v>
-      </c>
-      <c r="D20" s="14">
-        <v>4</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-25</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I20" s="14">
         <v>30</v>
@@ -1128,13 +1128,13 @@
         <v>-6.25</v>
       </c>
       <c r="L20" s="15">
-        <v>-16.666666666666</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="M20" s="15">
-        <v>-26.829268292682</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.461538461538</v>
+        <v>-89.583333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>64.705882352941</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H21" s="18">
-        <v>48.101265822784</v>
+        <v>50</v>
       </c>
       <c r="I21" s="17">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="J21" s="17">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="K21" s="18">
-        <v>23.728813559322</v>
+        <v>19.191919191919</v>
       </c>
       <c r="L21" s="18">
-        <v>28.070175438596</v>
+        <v>23.560209424083</v>
       </c>
       <c r="M21" s="18">
-        <v>-25</v>
+        <v>-26.479750778816</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.121878121878</v>
+        <v>-78.661844484629</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>-35</v>
+        <v>93.75</v>
       </c>
       <c r="F24" s="14">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="G24" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H24" s="15">
-        <v>24.561403508771</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I24" s="14">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="J24" s="14">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="K24" s="15">
-        <v>39.534883720930</v>
+        <v>46.896551724137</v>
       </c>
       <c r="L24" s="15">
-        <v>2.857142857142</v>
+        <v>3.902439024390</v>
       </c>
       <c r="M24" s="15">
-        <v>24.137931034482</v>
+        <v>25.294117647058</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>8</v>
+      </c>
+      <c r="D25" s="14">
         <v>3</v>
       </c>
-      <c r="D25" s="14">
-        <v>7</v>
-      </c>
       <c r="E25" s="15">
-        <v>-57.142857142857</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>-31.578947368421</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="I25" s="14">
+        <v>47</v>
+      </c>
+      <c r="J25" s="14">
         <v>39</v>
       </c>
-      <c r="J25" s="14">
-        <v>36</v>
-      </c>
       <c r="K25" s="15">
-        <v>8.333333333333</v>
+        <v>20.512820512820</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.415094339622</v>
+        <v>-32.857142857142</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F26" s="14">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G26" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H26" s="15">
+        <v>-5.357142857142</v>
+      </c>
+      <c r="I26" s="14">
+        <v>108</v>
+      </c>
+      <c r="J26" s="14">
+        <v>115</v>
+      </c>
+      <c r="K26" s="15">
+        <v>-6.086956521739</v>
+      </c>
+      <c r="L26" s="15">
         <v>0</v>
       </c>
-      <c r="I26" s="14">
-        <v>95</v>
-      </c>
-      <c r="J26" s="14">
-        <v>106</v>
-      </c>
-      <c r="K26" s="15">
-        <v>-10.377358490566</v>
-      </c>
-      <c r="L26" s="15">
-        <v>-5</v>
-      </c>
       <c r="M26" s="15">
-        <v>-15.178571428571</v>
+        <v>-18.796992481203</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1406,16 +1406,16 @@
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1431,32 +1431,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-71.428571428571</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J28" s="14">
         <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -905,31 +905,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>-88.235294117647</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
-      </c>
-      <c r="D16" s="14">
-        <v>4</v>
-      </c>
-      <c r="E16" s="15">
-        <v>25</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J16" s="14">
         <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>38.095238095238</v>
+        <v>47.619047619047</v>
       </c>
       <c r="L16" s="15">
-        <v>31.818181818181</v>
+        <v>29.166666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-46.296296296296</v>
+        <v>-47.457627118644</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.853658536585</v>
+        <v>-86.160714285714</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-42.857142857142</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>47.826086956521</v>
+        <v>20.833333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J17" s="14">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K17" s="15">
-        <v>6.349206349206</v>
+        <v>5.797101449275</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.898550724637</v>
+        <v>-2.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>36.734693877551</v>
+        <v>37.735849056603</v>
       </c>
       <c r="N17" s="15">
-        <v>-40.707964601769</v>
+        <v>-42.519685039370</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>2</v>
       </c>
       <c r="H18" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K18" s="15">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="L18" s="15">
-        <v>27.272727272727</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M18" s="15">
-        <v>-78.461538461538</v>
+        <v>-78.873239436619</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.967741935483</v>
+        <v>-91.124260355029</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>39.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J19" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K19" s="15">
-        <v>30.985915492957</v>
+        <v>29.333333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>86</v>
+        <v>73.214285714285</v>
       </c>
       <c r="M19" s="15">
-        <v>-14.678899082568</v>
+        <v>-14.159292035398</v>
       </c>
       <c r="N19" s="15">
-        <v>-71.028037383177</v>
+        <v>-73.055555555555</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15">
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
         <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="I20" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J20" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K20" s="15">
-        <v>-6.25</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="L20" s="15">
-        <v>-18.918918918918</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M20" s="15">
-        <v>-28.571428571428</v>
+        <v>-29.787234042553</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.583333333333</v>
+        <v>-89.877300613496</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.285714285714</v>
+        <v>30.769230769230</v>
       </c>
       <c r="F21" s="17">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="G21" s="17">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="I21" s="17">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="J21" s="17">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="K21" s="18">
-        <v>19.191919191919</v>
+        <v>19.905213270142</v>
       </c>
       <c r="L21" s="18">
-        <v>23.560209424083</v>
+        <v>18.779342723004</v>
       </c>
       <c r="M21" s="18">
-        <v>-26.479750778816</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.661844484629</v>
+        <v>-79.480940794809</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1235,11 +1235,11 @@
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-100</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
         <v>1</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
         <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>93.75</v>
+        <v>25</v>
       </c>
       <c r="F24" s="14">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G24" s="14">
         <v>63</v>
       </c>
       <c r="H24" s="15">
-        <v>44.444444444444</v>
+        <v>34.920634920634</v>
       </c>
       <c r="I24" s="14">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J24" s="14">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="K24" s="15">
-        <v>46.896551724137</v>
+        <v>44.720496894409</v>
       </c>
       <c r="L24" s="15">
-        <v>3.902439024390</v>
+        <v>4.484304932735</v>
       </c>
       <c r="M24" s="15">
-        <v>25.294117647058</v>
+        <v>27.322404371584</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>166.666666666667</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H25" s="15">
-        <v>-5.555555555555</v>
+        <v>35.714285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J25" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K25" s="15">
-        <v>20.512820512820</v>
+        <v>24.390243902439</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.857142857142</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
         <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>44.444444444444</v>
+        <v>77.777777777777</v>
       </c>
       <c r="F26" s="14">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.357142857142</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I26" s="14">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="J26" s="14">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.086956521739</v>
+        <v>-0.806451612903</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>3.361344537815</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.796992481203</v>
+        <v>-19.078947368421</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,32 +1390,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,25 +1438,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="I28" s="14">
         <v>6</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="I28" s="14">
-        <v>5</v>
       </c>
       <c r="J28" s="14">
         <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1472,26 +1472,26 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="15">
         <v>-100</v>
@@ -1513,26 +1513,26 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -863,8 +863,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -881,8 +881,8 @@
       <c r="K14" s="15">
         <v>0</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="15">
+        <v>0</v>
       </c>
       <c r="M14" s="15">
         <v>-50</v>
@@ -895,14 +895,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -917,19 +917,19 @@
         <v>3</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
+        <v>-25</v>
+      </c>
+      <c r="L15" s="15">
         <v>0</v>
       </c>
-      <c r="L15" s="15">
-        <v>50</v>
-      </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>-85</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -939,38 +939,38 @@
       <c r="C16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>33.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I16" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K16" s="15">
-        <v>47.619047619047</v>
+        <v>50</v>
       </c>
       <c r="L16" s="15">
-        <v>29.166666666666</v>
+        <v>17.857142857142</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.457627118644</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.160714285714</v>
+        <v>-86.419753086419</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-16.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H17" s="15">
-        <v>20.833333333333</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I17" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J17" s="14">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="K17" s="15">
-        <v>5.797101449275</v>
+        <v>1.298701298701</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.666666666666</v>
+        <v>-6.024096385542</v>
       </c>
       <c r="M17" s="15">
-        <v>37.735849056603</v>
+        <v>36.842105263157</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.519685039370</v>
+        <v>-44.680851063829</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
+        <v>5</v>
+      </c>
+      <c r="G18" s="14">
         <v>6</v>
       </c>
-      <c r="G18" s="14">
-        <v>2</v>
-      </c>
       <c r="H18" s="15">
-        <v>200</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K18" s="15">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="L18" s="15">
-        <v>7.142857142857</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M18" s="15">
-        <v>-78.873239436619</v>
+        <v>-76.315789473684</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.124260355029</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F19" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G19" s="14">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I19" s="14">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="J19" s="14">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K19" s="15">
-        <v>29.333333333333</v>
+        <v>34.615384615384</v>
       </c>
       <c r="L19" s="15">
-        <v>73.214285714285</v>
+        <v>77.966101694915</v>
       </c>
       <c r="M19" s="15">
-        <v>-14.159292035398</v>
+        <v>-16</v>
       </c>
       <c r="N19" s="15">
-        <v>-73.055555555555</v>
+        <v>-75.352112676056</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>40</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J20" s="14">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K20" s="15">
-        <v>-2.941176470588</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="L20" s="15">
-        <v>-21.428571428571</v>
+        <v>-22.448979591836</v>
       </c>
       <c r="M20" s="15">
-        <v>-29.787234042553</v>
+        <v>-25.490196078431</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.877300613496</v>
+        <v>-89.235127478753</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>30.769230769230</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F21" s="17">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H21" s="18">
-        <v>24</v>
+        <v>6.410256410256</v>
       </c>
       <c r="I21" s="17">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="J21" s="17">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="K21" s="18">
-        <v>19.905213270142</v>
+        <v>15.966386554621</v>
       </c>
       <c r="L21" s="18">
-        <v>18.779342723004</v>
+        <v>16.455696202531</v>
       </c>
       <c r="M21" s="18">
-        <v>-26.666666666666</v>
+        <v>-27.368421052631</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.480940794809</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1226,29 +1226,29 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-100</v>
       </c>
       <c r="I23" s="14">
         <v>1</v>
       </c>
       <c r="J23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="15">
         <v>-50</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>25</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="F24" s="14">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H24" s="15">
-        <v>34.920634920634</v>
+        <v>6.756756756756</v>
       </c>
       <c r="I24" s="14">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="J24" s="14">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="K24" s="15">
-        <v>44.720496894409</v>
+        <v>34.972677595628</v>
       </c>
       <c r="L24" s="15">
-        <v>4.484304932735</v>
+        <v>2.489626556016</v>
       </c>
       <c r="M24" s="15">
-        <v>27.322404371584</v>
+        <v>27.319587628866</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>-75</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>35.714285714285</v>
+        <v>-15</v>
       </c>
       <c r="I25" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J25" s="14">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K25" s="15">
-        <v>24.390243902439</v>
+        <v>8.163265306122</v>
       </c>
       <c r="L25" s="15">
-        <v>-29.166666666666</v>
+        <v>-26.388888888888</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>77.777777777777</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H26" s="15">
-        <v>18.181818181818</v>
+        <v>2.127659574468</v>
       </c>
       <c r="I26" s="14">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="J26" s="14">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.806451612903</v>
+        <v>-3.623188405797</v>
       </c>
       <c r="L26" s="15">
-        <v>3.361344537815</v>
+        <v>3.100775193798</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.078947368421</v>
+        <v>-22.674418604651</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,14 +1387,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1409,13 +1409,13 @@
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L27" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,14 +1428,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>5</v>
@@ -1450,10 +1450,10 @@
         <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>-60</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="L28" s="15">
         <v>20</v>
@@ -1472,11 +1472,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1513,11 +1513,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="15">
         <v>-50</v>
@@ -895,41 +895,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="M15" s="15">
+        <v>150</v>
       </c>
       <c r="N15" s="15">
-        <v>-85.714285714285</v>
+        <v>-79.166666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
         <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>57.142857142857</v>
+        <v>71.428571428571</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K16" s="15">
         <v>50</v>
       </c>
       <c r="L16" s="15">
-        <v>17.857142857142</v>
+        <v>16.129032258064</v>
       </c>
       <c r="M16" s="15">
-        <v>-52.173913043478</v>
+        <v>-51.351351351351</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.419753086419</v>
+        <v>-86.363636363636</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
+        <v>14</v>
+      </c>
+      <c r="G17" s="14">
+        <v>24</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-41.666666666666</v>
+      </c>
+      <c r="I17" s="14">
+        <v>80</v>
+      </c>
+      <c r="J17" s="14">
+        <v>80</v>
+      </c>
+      <c r="K17" s="15">
+        <v>0</v>
+      </c>
+      <c r="L17" s="15">
+        <v>-11.111111111111</v>
+      </c>
+      <c r="M17" s="15">
         <v>25</v>
       </c>
-      <c r="G17" s="14">
-        <v>26</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-3.846153846153</v>
-      </c>
-      <c r="I17" s="14">
-        <v>78</v>
-      </c>
-      <c r="J17" s="14">
-        <v>77</v>
-      </c>
-      <c r="K17" s="15">
-        <v>1.298701298701</v>
-      </c>
-      <c r="L17" s="15">
-        <v>-6.024096385542</v>
-      </c>
-      <c r="M17" s="15">
-        <v>36.842105263157</v>
-      </c>
       <c r="N17" s="15">
-        <v>-44.680851063829</v>
+        <v>-47.368421052631</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-16.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I18" s="14">
         <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K18" s="15">
-        <v>50</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L18" s="15">
         <v>28.571428571428</v>
       </c>
       <c r="M18" s="15">
-        <v>-76.315789473684</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.476190476190</v>
+        <v>-91.428571428571</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>166.666666666667</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="14">
         <v>22</v>
       </c>
       <c r="H19" s="15">
-        <v>27.272727272727</v>
+        <v>22.727272727272</v>
       </c>
       <c r="I19" s="14">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="J19" s="14">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K19" s="15">
-        <v>34.615384615384</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>77.966101694915</v>
+        <v>80.645161290322</v>
       </c>
       <c r="M19" s="15">
-        <v>-16</v>
+        <v>-17.037037037037</v>
       </c>
       <c r="N19" s="15">
-        <v>-75.352112676056</v>
+        <v>-76.170212765957</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J20" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.636363636363</v>
+        <v>-12.765957446808</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.448979591836</v>
+        <v>-21.153846153846</v>
       </c>
       <c r="M20" s="15">
-        <v>-25.490196078431</v>
+        <v>-26.785714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.235127478753</v>
+        <v>-89.210526315789</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.222222222222</v>
+        <v>13.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H21" s="18">
-        <v>6.410256410256</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I21" s="17">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J21" s="17">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="K21" s="18">
-        <v>15.966386554621</v>
+        <v>15.810276679841</v>
       </c>
       <c r="L21" s="18">
-        <v>16.455696202531</v>
+        <v>14.901960784313</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.368421052631</v>
+        <v>-29.227053140096</v>
       </c>
       <c r="N21" s="18">
-        <v>-80</v>
+        <v>-80.557398805574</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1226,11 +1226,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1254,7 +1254,7 @@
         <v>-50</v>
       </c>
       <c r="M23" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>-31.818181818181</v>
+        <v>30.769230769230</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G24" s="14">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H24" s="15">
-        <v>6.756756756756</v>
+        <v>25.373134328358</v>
       </c>
       <c r="I24" s="14">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="J24" s="14">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="K24" s="15">
-        <v>34.972677595628</v>
+        <v>35.204081632653</v>
       </c>
       <c r="L24" s="15">
-        <v>2.489626556016</v>
+        <v>3.921568627450</v>
       </c>
       <c r="M24" s="15">
-        <v>27.319587628866</v>
+        <v>28.019323671497</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
+        <v>16</v>
+      </c>
+      <c r="G25" s="14">
         <v>17</v>
       </c>
-      <c r="G25" s="14">
-        <v>20</v>
-      </c>
       <c r="H25" s="15">
-        <v>-15</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I25" s="14">
+        <v>55</v>
+      </c>
+      <c r="J25" s="14">
         <v>53</v>
       </c>
-      <c r="J25" s="14">
-        <v>49</v>
-      </c>
       <c r="K25" s="15">
-        <v>8.163265306122</v>
+        <v>3.773584905660</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.388888888888</v>
+        <v>-25.675675675675</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>11</v>
+      </c>
+      <c r="D26" s="14">
         <v>9</v>
       </c>
-      <c r="D26" s="14">
-        <v>14</v>
-      </c>
       <c r="E26" s="15">
-        <v>-35.714285714285</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F26" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>2.127659574468</v>
+        <v>21.951219512195</v>
       </c>
       <c r="I26" s="14">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="J26" s="14">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.623188405797</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="L26" s="15">
-        <v>3.100775193798</v>
+        <v>3.597122302158</v>
       </c>
       <c r="M26" s="15">
-        <v>-22.674418604651</v>
+        <v>-20.879120879120</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>-20</v>
+        <v>40</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1431,20 +1431,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>3</v>
+      </c>
+      <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>5</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
       <c r="H28" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
         <v>6</v>
@@ -1456,7 +1456,7 @@
         <v>-64.705882352941</v>
       </c>
       <c r="L28" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,32 +1478,32 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
         <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-97.435897435897</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,32 +1519,32 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-96.875</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1554,29 +1554,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>100</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -896,7 +896,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -914,22 +914,22 @@
         <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-79.166666666666</v>
+        <v>-76</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>4</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="14">
+        <v>11</v>
+      </c>
+      <c r="G16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>50</v>
-      </c>
-      <c r="F16" s="14">
-        <v>12</v>
-      </c>
-      <c r="G16" s="14">
-        <v>7</v>
-      </c>
       <c r="H16" s="15">
-        <v>71.428571428571</v>
+        <v>266.666666666667</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J16" s="14">
         <v>24</v>
       </c>
       <c r="K16" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>16.129032258064</v>
+        <v>17.647058823529</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.351351351351</v>
+        <v>-49.367088607594</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.363636363636</v>
+        <v>-86.013986013986</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H17" s="15">
-        <v>-41.666666666666</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="I17" s="14">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J17" s="14">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>-3.370786516853</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.111111111111</v>
+        <v>-11.340206185567</v>
       </c>
       <c r="M17" s="15">
-        <v>25</v>
+        <v>22.857142857142</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.368421052631</v>
+        <v>-46.913580246913</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1021,20 +1021,20 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
         <v>18</v>
@@ -1046,13 +1046,13 @@
         <v>38.461538461538</v>
       </c>
       <c r="L18" s="15">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>-77.777777777777</v>
+        <v>-79.310344827586</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.428571428571</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>16.666666666666</v>
+        <v>300</v>
       </c>
       <c r="F19" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H19" s="15">
-        <v>22.727272727272</v>
+        <v>86.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J19" s="14">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K19" s="15">
-        <v>33.333333333333</v>
+        <v>41.860465116279</v>
       </c>
       <c r="L19" s="15">
-        <v>80.645161290322</v>
+        <v>79.411764705882</v>
       </c>
       <c r="M19" s="15">
-        <v>-17.037037037037</v>
+        <v>-17.567567567567</v>
       </c>
       <c r="N19" s="15">
-        <v>-76.170212765957</v>
+        <v>-80.130293159609</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>-20</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I20" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J20" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K20" s="15">
-        <v>-12.765957446808</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="L20" s="15">
-        <v>-21.153846153846</v>
+        <v>-17.543859649122</v>
       </c>
       <c r="M20" s="15">
-        <v>-26.785714285714</v>
+        <v>-18.965517241379</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.210526315789</v>
+        <v>-88.809523809523</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>13.333333333333</v>
+        <v>84.615384615384</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="G21" s="17">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.263157894736</v>
+        <v>19.117647058823</v>
       </c>
       <c r="I21" s="17">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="J21" s="17">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="K21" s="18">
-        <v>15.810276679841</v>
+        <v>20.300751879699</v>
       </c>
       <c r="L21" s="18">
-        <v>14.901960784313</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M21" s="18">
-        <v>-29.227053140096</v>
+        <v>-28.411633109619</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.557398805574</v>
+        <v>-81.693363844393</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1232,29 +1232,29 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="F23" s="14">
+        <v>1</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="14">
         <v>2</v>
       </c>
       <c r="K23" s="15">
+        <v>0</v>
+      </c>
+      <c r="L23" s="15">
+        <v>0</v>
+      </c>
+      <c r="M23" s="15">
         <v>-50</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-50</v>
-      </c>
-      <c r="M23" s="15">
-        <v>-75</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>30.769230769230</v>
+        <v>-5</v>
       </c>
       <c r="F24" s="14">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H24" s="15">
-        <v>25.373134328358</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="J24" s="14">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="K24" s="15">
-        <v>35.204081632653</v>
+        <v>31.944444444444</v>
       </c>
       <c r="L24" s="15">
-        <v>3.921568627450</v>
+        <v>3.260869565217</v>
       </c>
       <c r="M24" s="15">
-        <v>28.019323671497</v>
+        <v>23.376623376623</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F25" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>-5.882352941176</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="I25" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J25" s="14">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K25" s="15">
-        <v>3.773584905660</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.675675675675</v>
+        <v>-30</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>19</v>
+      </c>
+      <c r="D26" s="14">
         <v>11</v>
       </c>
-      <c r="D26" s="14">
-        <v>9</v>
-      </c>
       <c r="E26" s="15">
-        <v>22.222222222222</v>
+        <v>72.727272727272</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G26" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>21.951219512195</v>
+        <v>25.581395348837</v>
       </c>
       <c r="I26" s="14">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="J26" s="14">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.040816326530</v>
+        <v>2.531645569620</v>
       </c>
       <c r="L26" s="15">
-        <v>3.597122302158</v>
+        <v>10.204081632653</v>
       </c>
       <c r="M26" s="15">
-        <v>-20.879120879120</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,34 +1388,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
+        <v>2</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-64.705882352941</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,10 +1500,10 @@
         <v>-80</v>
       </c>
       <c r="M29" s="15">
-        <v>-90.909090909090</v>
+        <v>-92.307692307692</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.435897435897</v>
+        <v>-97.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,10 +1541,10 @@
         <v>-80</v>
       </c>
       <c r="M30" s="15">
-        <v>-88.888888888888</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.875</v>
+        <v>-96.969696969697</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1637,8 +1637,8 @@
       <c r="K33" s="15">
         <v>-100</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,8 +854,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -863,8 +863,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -873,22 +873,22 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
+        <v>100</v>
+      </c>
+      <c r="L14" s="15">
         <v>0</v>
       </c>
-      <c r="L14" s="15">
-        <v>-50</v>
-      </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-85.714285714285</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -914,22 +914,22 @@
         <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-76</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>266.666666666667</v>
+        <v>100</v>
       </c>
       <c r="I16" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J16" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>66.666666666666</v>
+        <v>57.692307692307</v>
       </c>
       <c r="L16" s="15">
-        <v>17.647058823529</v>
+        <v>10.810810810810</v>
       </c>
       <c r="M16" s="15">
-        <v>-49.367088607594</v>
+        <v>-53.409090909090</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.013986013986</v>
+        <v>-86.731391585760</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
         <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-44.444444444444</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>-34.615384615384</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="I17" s="14">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="J17" s="14">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.370786516853</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.340206185567</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="M17" s="15">
-        <v>22.857142857142</v>
+        <v>21.518987341772</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.913580246913</v>
+        <v>-44.827586206896</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1021,38 +1021,38 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I18" s="14">
         <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K18" s="15">
-        <v>38.461538461538</v>
+        <v>20</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.310344827586</v>
+        <v>-82.178217821782</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.307692307692</v>
+        <v>-92.682926829268</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H19" s="15">
-        <v>86.666666666666</v>
+        <v>122.222222222222</v>
       </c>
       <c r="I19" s="14">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J19" s="14">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="K19" s="15">
-        <v>41.860465116279</v>
+        <v>49.462365591397</v>
       </c>
       <c r="L19" s="15">
-        <v>79.411764705882</v>
+        <v>85.333333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>-17.567567567567</v>
+        <v>-13.125</v>
       </c>
       <c r="N19" s="15">
-        <v>-80.130293159609</v>
+        <v>-81.782437745740</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G20" s="14">
         <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>5.882352941176</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I20" s="14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J20" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K20" s="15">
-        <v>-4.081632653061</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L20" s="15">
-        <v>-17.543859649122</v>
+        <v>-20</v>
       </c>
       <c r="M20" s="15">
-        <v>-18.965517241379</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.809523809523</v>
+        <v>-89.309576837416</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>84.615384615384</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F21" s="17">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H21" s="18">
-        <v>19.117647058823</v>
+        <v>22.077922077922</v>
       </c>
       <c r="I21" s="17">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="J21" s="17">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="K21" s="18">
-        <v>20.300751879699</v>
+        <v>21.875</v>
       </c>
       <c r="L21" s="18">
-        <v>14.285714285714</v>
+        <v>15.841584158415</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.411633109619</v>
+        <v>-29.940119760479</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.693363844393</v>
+        <v>-82.218844984802</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1232,14 +1232,14 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="14">
-        <v>1</v>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I23" s="14">
         <v>2</v>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M23" s="15">
         <v>-50</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>-5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G24" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="I24" s="14">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="J24" s="14">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="K24" s="15">
-        <v>31.944444444444</v>
+        <v>24.894514767932</v>
       </c>
       <c r="L24" s="15">
-        <v>3.260869565217</v>
+        <v>-2.950819672131</v>
       </c>
       <c r="M24" s="15">
-        <v>23.376623376623</v>
+        <v>15.175097276264</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
         <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-85.714285714285</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F25" s="14">
         <v>8</v>
       </c>
       <c r="G25" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H25" s="15">
-        <v>-61.904761904761</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I25" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J25" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.666666666666</v>
+        <v>-11.940298507462</v>
       </c>
       <c r="L25" s="15">
-        <v>-30</v>
+        <v>-35.869565217391</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>72.727272727272</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>25.581395348837</v>
+        <v>6.122448979591</v>
       </c>
       <c r="I26" s="14">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="J26" s="14">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="K26" s="15">
-        <v>2.531645569620</v>
+        <v>1.734104046242</v>
       </c>
       <c r="L26" s="15">
-        <v>10.204081632653</v>
+        <v>12.820512820512</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.285714285714</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,29 +1390,29 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>66.666666666666</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1428,32 +1428,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I28" s="14">
         <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>-61.111111111111</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="L28" s="15">
         <v>-12.5</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1479,39 +1479,39 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="M29" s="15">
-        <v>-92.307692307692</v>
+        <v>-86.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.5</v>
+        <v>-95.555555555555</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1520,31 +1520,31 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="M30" s="15">
-        <v>-90.909090909090</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.969696969697</v>
+        <v>-94.594594594594</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -864,7 +864,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -873,22 +873,22 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,7 +896,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,31 +905,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>300</v>
+        <v>7</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="M15" s="15">
-        <v>133.333333333333</v>
+        <v>150</v>
       </c>
       <c r="N15" s="15">
-        <v>-72</v>
+        <v>-64.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-50</v>
+        <v>3</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="I16" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J16" s="14">
         <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>57.692307692307</v>
+        <v>69.230769230769</v>
       </c>
       <c r="L16" s="15">
-        <v>10.810810810810</v>
+        <v>12.820512820512</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.409090909090</v>
+        <v>-51.648351648351</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.731391585760</v>
+        <v>-86.292834890965</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-11.111111111111</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H17" s="15">
-        <v>-24.137931034482</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="J17" s="14">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.040816326530</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.571428571428</v>
+        <v>-6.422018348623</v>
       </c>
       <c r="M17" s="15">
-        <v>21.518987341772</v>
+        <v>22.891566265060</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.827586206896</v>
+        <v>-45.454545454545</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="15">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="L18" s="15">
-        <v>-10</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="M18" s="15">
-        <v>-82.178217821782</v>
+        <v>-82.568807339449</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.682926829268</v>
+        <v>-92.748091603053</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
         <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G19" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H19" s="15">
-        <v>122.222222222222</v>
+        <v>104.761904761905</v>
       </c>
       <c r="I19" s="14">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="J19" s="14">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K19" s="15">
-        <v>49.462365591397</v>
+        <v>52.525252525252</v>
       </c>
       <c r="L19" s="15">
-        <v>85.333333333333</v>
+        <v>86.419753086419</v>
       </c>
       <c r="M19" s="15">
-        <v>-13.125</v>
+        <v>-11.176470588235</v>
       </c>
       <c r="N19" s="15">
-        <v>-81.782437745740</v>
+        <v>-82.683486238532</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>-11.764705882352</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J20" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K20" s="15">
-        <v>-5.882352941176</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="L20" s="15">
-        <v>-20</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="M20" s="15">
-        <v>-29.411764705882</v>
+        <v>-29.577464788732</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.309576837416</v>
+        <v>-89.837398373983</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>18.181818181818</v>
+        <v>75</v>
       </c>
       <c r="F21" s="17">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G21" s="17">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>22.077922077922</v>
+        <v>51.515151515151</v>
       </c>
       <c r="I21" s="17">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="J21" s="17">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="K21" s="18">
-        <v>21.875</v>
+        <v>24.671052631578</v>
       </c>
       <c r="L21" s="18">
-        <v>15.841584158415</v>
+        <v>16.975308641975</v>
       </c>
       <c r="M21" s="18">
-        <v>-29.940119760479</v>
+        <v>-28.625235404896</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.218844984802</v>
+        <v>-82.542607093505</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1235,11 +1235,11 @@
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-100</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
         <v>2</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>8.695652173913</v>
       </c>
       <c r="F24" s="14">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="G24" s="14">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H24" s="15">
-        <v>-18.421052631578</v>
+        <v>-5.194805194805</v>
       </c>
       <c r="I24" s="14">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="J24" s="14">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="K24" s="15">
-        <v>24.894514767932</v>
+        <v>23.461538461538</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.950819672131</v>
+        <v>-0.310559006211</v>
       </c>
       <c r="M24" s="15">
-        <v>15.175097276264</v>
+        <v>13.028169014084</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>-71.428571428571</v>
+        <v>-30</v>
       </c>
       <c r="F25" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H25" s="15">
-        <v>-69.230769230769</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J25" s="14">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.940298507462</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L25" s="15">
-        <v>-35.869565217391</v>
+        <v>-31.958762886597</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-6.666666666666</v>
+        <v>150</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G26" s="14">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>6.122448979591</v>
+        <v>41.463414634146</v>
       </c>
       <c r="I26" s="14">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="J26" s="14">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="K26" s="15">
-        <v>1.734104046242</v>
+        <v>6.703910614525</v>
       </c>
       <c r="L26" s="15">
-        <v>12.820512820512</v>
+        <v>11.046511627907</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.384615384615</v>
+        <v>-14.349775784753</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,34 +1388,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>8</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <v>5</v>
-      </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-63.157894736842</v>
+        <v>-65</v>
       </c>
       <c r="L28" s="15">
-        <v>-12.5</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1488,22 +1488,22 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L29" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="M29" s="15">
-        <v>-86.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.555555555555</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1529,22 +1529,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L30" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="M30" s="15">
-        <v>-84.615384615384</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.594594594594</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,8 +854,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>3</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -929,7 +929,7 @@
         <v>150</v>
       </c>
       <c r="N15" s="15">
-        <v>-64.285714285714</v>
+        <v>-65.517241379310</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>10</v>
+      </c>
+      <c r="G16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="14">
-        <v>11</v>
-      </c>
-      <c r="G16" s="14">
-        <v>4</v>
-      </c>
       <c r="H16" s="15">
-        <v>175</v>
+        <v>233.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K16" s="15">
-        <v>69.230769230769</v>
+        <v>70.370370370370</v>
       </c>
       <c r="L16" s="15">
-        <v>12.820512820512</v>
+        <v>9.523809523809</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.648351648351</v>
+        <v>-53.535353535353</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.292834890965</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-14.285714285714</v>
+        <v>350</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G17" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>-14.285714285714</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I17" s="14">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J17" s="14">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.857142857142</v>
+        <v>4.672897196261</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.422018348623</v>
+        <v>-2.608695652173</v>
       </c>
       <c r="M17" s="15">
-        <v>22.891566265060</v>
+        <v>24.444444444444</v>
       </c>
       <c r="N17" s="15">
-        <v>-45.454545454545</v>
+        <v>-45.098039215686</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
+        <v>100</v>
+      </c>
+      <c r="F18" s="14">
+        <v>5</v>
+      </c>
+      <c r="G18" s="14">
+        <v>5</v>
+      </c>
+      <c r="H18" s="15">
         <v>0</v>
       </c>
-      <c r="F18" s="14">
-        <v>1</v>
-      </c>
-      <c r="G18" s="14">
-        <v>4</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-75</v>
-      </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K18" s="15">
-        <v>18.75</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L18" s="15">
-        <v>-17.391304347826</v>
+        <v>-8</v>
       </c>
       <c r="M18" s="15">
-        <v>-82.568807339449</v>
+        <v>-80.172413793103</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.748091603053</v>
+        <v>-92.068965517241</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
         <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>216.666666666667</v>
       </c>
       <c r="F19" s="14">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G19" s="14">
         <v>21</v>
       </c>
       <c r="H19" s="15">
-        <v>104.761904761905</v>
+        <v>161.904761904762</v>
       </c>
       <c r="I19" s="14">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="J19" s="14">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K19" s="15">
-        <v>52.525252525252</v>
+        <v>62.857142857142</v>
       </c>
       <c r="L19" s="15">
-        <v>86.419753086419</v>
+        <v>96.551724137931</v>
       </c>
       <c r="M19" s="15">
-        <v>-11.176470588235</v>
+        <v>-8.556149732620</v>
       </c>
       <c r="N19" s="15">
-        <v>-82.683486238532</v>
+        <v>-82.848545636910</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
         <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I20" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J20" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K20" s="15">
-        <v>-5.660377358490</v>
+        <v>-1.785714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.242424242424</v>
+        <v>-19.117647058823</v>
       </c>
       <c r="M20" s="15">
-        <v>-29.577464788732</v>
+        <v>-27.631578947368</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.837398373983</v>
+        <v>-89.382239382239</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>75</v>
+        <v>171.428571428571</v>
       </c>
       <c r="F21" s="17">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="G21" s="17">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H21" s="18">
-        <v>51.515151515151</v>
+        <v>86.153846153846</v>
       </c>
       <c r="I21" s="17">
-        <v>379</v>
+        <v>420</v>
       </c>
       <c r="J21" s="17">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="K21" s="18">
-        <v>24.671052631578</v>
+        <v>32.075471698113</v>
       </c>
       <c r="L21" s="18">
-        <v>16.975308641975</v>
+        <v>22.448979591836</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.625235404896</v>
+        <v>-26.956521739130</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.542607093505</v>
+        <v>-82.441471571906</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>8.695652173913</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="F24" s="14">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G24" s="14">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.194805194805</v>
+        <v>-18.604651162790</v>
       </c>
       <c r="I24" s="14">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="J24" s="14">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="K24" s="15">
-        <v>23.461538461538</v>
+        <v>18.794326241134</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.310559006211</v>
+        <v>-2.616279069767</v>
       </c>
       <c r="M24" s="15">
-        <v>13.028169014084</v>
+        <v>8.414239482200</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-30</v>
+        <v>-62.5</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H25" s="15">
-        <v>-53.571428571428</v>
+        <v>-56.25</v>
       </c>
       <c r="I25" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J25" s="14">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K25" s="15">
-        <v>-14.285714285714</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L25" s="15">
-        <v>-31.958762886597</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>150</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F26" s="14">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G26" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>41.463414634146</v>
+        <v>46.511627906976</v>
       </c>
       <c r="I26" s="14">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="J26" s="14">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="K26" s="15">
-        <v>6.703910614525</v>
+        <v>8.421052631578</v>
       </c>
       <c r="L26" s="15">
-        <v>11.046511627907</v>
+        <v>13.812154696132</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.349775784753</v>
+        <v>-13.807531380753</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,13 +1397,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="I27" s="14">
         <v>12</v>
@@ -1415,7 +1415,7 @@
         <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
         <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-65</v>
+        <v>-45</v>
       </c>
       <c r="L28" s="15">
-        <v>-36.363636363636</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1510,8 +1510,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1563,11 +1563,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
@@ -1613,26 +1613,26 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -895,41 +895,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>100</v>
       </c>
       <c r="F15" s="14">
+        <v>6</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>500</v>
+      </c>
+      <c r="I15" s="14">
+        <v>12</v>
+      </c>
+      <c r="J15" s="14">
         <v>5</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="14">
-        <v>10</v>
-      </c>
-      <c r="J15" s="14">
-        <v>4</v>
-      </c>
       <c r="K15" s="15">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="L15" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-65.517241379310</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>233.333333333333</v>
+        <v>60</v>
       </c>
       <c r="I16" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J16" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K16" s="15">
-        <v>70.370370370370</v>
+        <v>65.517241379310</v>
       </c>
       <c r="L16" s="15">
-        <v>9.523809523809</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.535353535353</v>
+        <v>-54.285714285714</v>
       </c>
       <c r="N16" s="15">
         <v>-86.666666666666</v>
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>350</v>
+        <v>-90</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H17" s="15">
-        <v>11.111111111111</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I17" s="14">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J17" s="14">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K17" s="15">
-        <v>4.672897196261</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.608695652173</v>
+        <v>-6.557377049180</v>
       </c>
       <c r="M17" s="15">
-        <v>24.444444444444</v>
+        <v>20</v>
       </c>
       <c r="N17" s="15">
-        <v>-45.098039215686</v>
+        <v>-48.181818181818</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
-      </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J18" s="14">
         <v>18</v>
       </c>
       <c r="K18" s="15">
-        <v>27.777777777777</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-8</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M18" s="15">
-        <v>-80.172413793103</v>
+        <v>-80.165289256198</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.068965517241</v>
+        <v>-92.258064516129</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>216.666666666667</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G19" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>161.904761904762</v>
+        <v>88.888888888888</v>
       </c>
       <c r="I19" s="14">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J19" s="14">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="K19" s="15">
-        <v>62.857142857142</v>
+        <v>55.752212389380</v>
       </c>
       <c r="L19" s="15">
-        <v>96.551724137931</v>
+        <v>91.304347826087</v>
       </c>
       <c r="M19" s="15">
-        <v>-8.556149732620</v>
+        <v>-13.300492610837</v>
       </c>
       <c r="N19" s="15">
-        <v>-82.848545636910</v>
+        <v>-83.926940639269</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>55.555555555555</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I20" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J20" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K20" s="15">
-        <v>-1.785714285714</v>
+        <v>-4.838709677419</v>
       </c>
       <c r="L20" s="15">
-        <v>-19.117647058823</v>
+        <v>-15.714285714285</v>
       </c>
       <c r="M20" s="15">
-        <v>-27.631578947368</v>
+        <v>-30.588235294117</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.382239382239</v>
+        <v>-89.388489208633</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>171.428571428571</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F21" s="17">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="G21" s="17">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>86.153846153846</v>
+        <v>40.506329113924</v>
       </c>
       <c r="I21" s="17">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="J21" s="17">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="K21" s="18">
-        <v>32.075471698113</v>
+        <v>26.376811594202</v>
       </c>
       <c r="L21" s="18">
-        <v>22.448979591836</v>
+        <v>21.111111111111</v>
       </c>
       <c r="M21" s="18">
-        <v>-26.956521739130</v>
+        <v>-29.449838187702</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.441471571906</v>
+        <v>-83.100775193798</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1226,29 +1226,29 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="14">
+        <v>2</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-100</v>
       </c>
       <c r="I23" s="14">
         <v>2</v>
       </c>
       <c r="J23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="15">
         <v>-33.333333333333</v>
@@ -1268,34 +1268,34 @@
         <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-31.818181818181</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="F24" s="14">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G24" s="14">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H24" s="15">
-        <v>-18.604651162790</v>
+        <v>-25</v>
       </c>
       <c r="I24" s="14">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="J24" s="14">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="K24" s="15">
-        <v>18.794326241134</v>
+        <v>13.961038961039</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.616279069767</v>
+        <v>-3.038674033149</v>
       </c>
       <c r="M24" s="15">
-        <v>8.414239482200</v>
+        <v>5.405405405405</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
         <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-62.5</v>
+        <v>-87.5</v>
       </c>
       <c r="F25" s="14">
         <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H25" s="15">
-        <v>-56.25</v>
+        <v>-57.575757575757</v>
       </c>
       <c r="I25" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J25" s="14">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K25" s="15">
-        <v>-17.647058823529</v>
+        <v>-23.655913978494</v>
       </c>
       <c r="L25" s="15">
-        <v>-28.571428571428</v>
+        <v>-32.380952380952</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>46.511627906976</v>
+        <v>25</v>
       </c>
       <c r="I26" s="14">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="J26" s="14">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="K26" s="15">
-        <v>8.421052631578</v>
+        <v>7.425742574257</v>
       </c>
       <c r="L26" s="15">
-        <v>13.812154696132</v>
+        <v>9.595959595959</v>
       </c>
       <c r="M26" s="15">
-        <v>-13.807531380753</v>
+        <v>-16.538461538461</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
         <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>500</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>266.666666666667</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>-45</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>30.769230769230</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,10 +1500,10 @@
         <v>-40</v>
       </c>
       <c r="M29" s="15">
-        <v>-80</v>
+        <v>-81.25</v>
       </c>
       <c r="N29" s="15">
-        <v>-94</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,10 +1541,10 @@
         <v>-40</v>
       </c>
       <c r="M30" s="15">
-        <v>-76.923076923076</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.857142857142</v>
+        <v>-93.023255813953</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1613,11 +1613,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-113pct.xlsx
+++ b/data/source/weekly/cs-en-us-113pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -864,7 +864,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -882,13 +882,13 @@
         <v>200</v>
       </c>
       <c r="L14" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-66.666666666666</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,40 +896,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
         <v>2</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
         <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>140</v>
+        <v>85.714285714285</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>116.666666666667</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>116.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>-60</v>
+        <v>-62.857142857142</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>60</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J16" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>65.517241379310</v>
+        <v>59.375</v>
       </c>
       <c r="L16" s="15">
-        <v>9.090909090909</v>
+        <v>10.869565217391</v>
       </c>
       <c r="M16" s="15">
-        <v>-54.285714285714</v>
+        <v>-53.636363636363</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.666666666666</v>
+        <v>-86.472148541114</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-90</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H17" s="15">
-        <v>-7.142857142857</v>
+        <v>-24</v>
       </c>
       <c r="I17" s="14">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J17" s="14">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.564102564102</v>
+        <v>-5.691056910569</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.557377049180</v>
+        <v>-10.077519379845</v>
       </c>
       <c r="M17" s="15">
-        <v>20</v>
+        <v>19.587628865979</v>
       </c>
       <c r="N17" s="15">
-        <v>-48.181818181818</v>
+        <v>-50.427350427350</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
         <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="I18" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J18" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K18" s="15">
-        <v>33.333333333333</v>
+        <v>35</v>
       </c>
       <c r="L18" s="15">
-        <v>-7.692307692307</v>
+        <v>3.846153846153</v>
       </c>
       <c r="M18" s="15">
-        <v>-80.165289256198</v>
+        <v>-78.225806451612</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.258064516129</v>
+        <v>-91.793313069908</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1069,31 +1069,31 @@
         <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>88.888888888888</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I19" s="14">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="J19" s="14">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="K19" s="15">
-        <v>55.752212389380</v>
+        <v>50.413223140495</v>
       </c>
       <c r="L19" s="15">
-        <v>91.304347826087</v>
+        <v>89.583333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>-13.300492610837</v>
+        <v>-15.740740740740</v>
       </c>
       <c r="N19" s="15">
-        <v>-83.926940639269</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H20" s="15">
-        <v>-7.692307692307</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="I20" s="14">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J20" s="14">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K20" s="15">
-        <v>-4.838709677419</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.714285714285</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M20" s="15">
-        <v>-30.588235294117</v>
+        <v>-26.966292134831</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.388489208633</v>
+        <v>-88.926746166950</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-44.444444444444</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="F21" s="17">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H21" s="18">
-        <v>40.506329113924</v>
+        <v>22.093023255814</v>
       </c>
       <c r="I21" s="17">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="J21" s="17">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="K21" s="18">
-        <v>26.376811594202</v>
+        <v>22.192513368984</v>
       </c>
       <c r="L21" s="18">
-        <v>21.111111111111</v>
+        <v>21.542553191489</v>
       </c>
       <c r="M21" s="18">
-        <v>-29.449838187702</v>
+        <v>-29.147286821705</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.100775193798</v>
+        <v>-83.411978221415</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
         <v>-100</v>
@@ -1245,10 +1245,10 @@
         <v>2</v>
       </c>
       <c r="J23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L23" s="15">
         <v>-33.333333333333</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-42.307692307692</v>
+        <v>30</v>
       </c>
       <c r="F24" s="14">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="G24" s="14">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H24" s="15">
-        <v>-25</v>
+        <v>-10.989010989011</v>
       </c>
       <c r="I24" s="14">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="J24" s="14">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="K24" s="15">
-        <v>13.961038961039</v>
+        <v>15.243902439024</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.038674033149</v>
+        <v>-0.526315789473</v>
       </c>
       <c r="M24" s="15">
-        <v>5.405405405405</v>
+        <v>6.179775280898</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-87.5</v>
+        <v>20</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G25" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H25" s="15">
-        <v>-57.575757575757</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="I25" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J25" s="14">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K25" s="15">
-        <v>-23.655913978494</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.380952380952</v>
+        <v>-29.357798165137</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F26" s="14">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>25</v>
+        <v>30.555555555555</v>
       </c>
       <c r="I26" s="14">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="J26" s="14">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="K26" s="15">
-        <v>7.425742574257</v>
+        <v>6.698564593301</v>
       </c>
       <c r="L26" s="15">
-        <v>9.595959595959</v>
+        <v>5.188679245283</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.538461538461</v>
+        <v>-19.494584837545</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,34 +1388,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
         <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>6</v>
-      </c>
-      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="15">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>12</v>
+      </c>
+      <c r="G28" s="14">
+        <v>2</v>
+      </c>
+      <c r="H28" s="15">
         <v>500</v>
       </c>
-      <c r="F28" s="14">
-        <v>11</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
-      <c r="H28" s="15">
-        <v>266.666666666667</v>
-      </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
         <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>-19.047619047619</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>30.769230769230</v>
+        <v>38.461538461538</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1472,38 +1472,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="L29" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
         <v>-81.25</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.339622641509</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1513,38 +1513,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="L30" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
         <v>-78.571428571428</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.023255813953</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
